--- a/LineClass/level_shift_report.xlsx
+++ b/LineClass/level_shift_report.xlsx
@@ -1902,7 +1902,7 @@
         <v>-0.078</v>
       </c>
       <c r="N20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>0.918</v>
+        <v>0.93</v>
       </c>
       <c r="S20" t="n">
         <v>0.983</v>
@@ -2632,7 +2632,7 @@
         <v>0.117</v>
       </c>
       <c r="N30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O30" t="n">
         <v>10</v>
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>0.865</v>
+        <v>0.881</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -22120,7 +22120,7 @@
         <v>0</v>
       </c>
       <c r="W287" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="X287" t="inlineStr"/>
       <c r="Y287" t="inlineStr"/>
@@ -23523,13 +23523,13 @@
         <v>0.823</v>
       </c>
       <c r="N305" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O305" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P305" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q305" t="inlineStr">
         <is>
@@ -23537,13 +23537,13 @@
         </is>
       </c>
       <c r="R305" t="n">
-        <v>0.886</v>
+        <v>0.884</v>
       </c>
       <c r="S305" t="n">
-        <v>0.954</v>
+        <v>1</v>
       </c>
       <c r="T305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U305" t="n">
         <v>0</v>
@@ -24481,10 +24481,10 @@
         <v>-0.028</v>
       </c>
       <c r="N317" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O317" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P317" t="n">
         <v>4</v>
@@ -24495,7 +24495,7 @@
         </is>
       </c>
       <c r="R317" t="n">
-        <v>0.758</v>
+        <v>0.788</v>
       </c>
       <c r="S317" t="n">
         <v>0.948</v>
@@ -24647,7 +24647,7 @@
         <v>-0.502</v>
       </c>
       <c r="N319" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O319" t="n">
         <v>10</v>
@@ -24661,7 +24661,7 @@
         </is>
       </c>
       <c r="R319" t="n">
-        <v>0.503</v>
+        <v>0.52</v>
       </c>
       <c r="S319" t="n">
         <v>0.7</v>
@@ -25311,10 +25311,10 @@
         <v>-0.234</v>
       </c>
       <c r="N327" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O327" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P327" t="n">
         <v>2</v>
@@ -25325,7 +25325,7 @@
         </is>
       </c>
       <c r="R327" t="n">
-        <v>0.641</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="S327" t="n">
         <v>0.971</v>
@@ -25892,10 +25892,10 @@
         <v>0.915</v>
       </c>
       <c r="N334" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O334" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P334" t="n">
         <v>2</v>
@@ -25906,7 +25906,7 @@
         </is>
       </c>
       <c r="R334" t="n">
-        <v>0.477</v>
+        <v>0.505</v>
       </c>
       <c r="S334" t="n">
         <v>1</v>
@@ -26224,10 +26224,10 @@
         <v>0.159</v>
       </c>
       <c r="N338" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O338" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P338" t="n">
         <v>3</v>
@@ -26238,7 +26238,7 @@
         </is>
       </c>
       <c r="R338" t="n">
-        <v>0.626</v>
+        <v>0.646</v>
       </c>
       <c r="S338" t="n">
         <v>1</v>
@@ -26473,10 +26473,10 @@
         <v>0.46</v>
       </c>
       <c r="N341" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O341" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P341" t="n">
         <v>2</v>
@@ -26487,7 +26487,7 @@
         </is>
       </c>
       <c r="R341" t="n">
-        <v>0.516</v>
+        <v>0.539</v>
       </c>
       <c r="S341" t="n">
         <v>1</v>
@@ -26718,7 +26718,7 @@
         <v>0.117</v>
       </c>
       <c r="N344" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O344" t="n">
         <v>10</v>
@@ -26735,10 +26735,10 @@
         <v>0.955</v>
       </c>
       <c r="S344" t="n">
-        <v>0.964</v>
+        <v>0.965</v>
       </c>
       <c r="T344" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U344" t="inlineStr"/>
       <c r="V344" t="inlineStr"/>
@@ -27156,7 +27156,7 @@
         <v>0.039</v>
       </c>
       <c r="N350" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O350" t="n">
         <v>10</v>
@@ -27448,7 +27448,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="N354" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O354" t="n">
         <v>10</v>
@@ -28480,7 +28480,7 @@
         <v>-0.054</v>
       </c>
       <c r="N368" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O368" t="n">
         <v>10</v>
@@ -28494,7 +28494,7 @@
         </is>
       </c>
       <c r="R368" t="n">
-        <v>0.947</v>
+        <v>0.948</v>
       </c>
       <c r="S368" t="n">
         <v>0.969</v>
@@ -28924,7 +28924,7 @@
         <v>-0.45</v>
       </c>
       <c r="N374" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O374" t="n">
         <v>10</v>
@@ -28938,7 +28938,7 @@
         </is>
       </c>
       <c r="R374" t="n">
-        <v>0.884</v>
+        <v>0.885</v>
       </c>
       <c r="S374" t="n">
         <v>0.905</v>
@@ -29453,7 +29453,7 @@
         <v>-0.618</v>
       </c>
       <c r="N381" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O381" t="n">
         <v>10</v>
@@ -29599,7 +29599,7 @@
         <v>-0.168</v>
       </c>
       <c r="N383" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O383" t="n">
         <v>10</v>
@@ -29613,7 +29613,7 @@
         </is>
       </c>
       <c r="R383" t="n">
-        <v>0.977</v>
+        <v>0.978</v>
       </c>
       <c r="S383" t="n">
         <v>0.986</v>
@@ -29818,7 +29818,7 @@
         <v>-0.12</v>
       </c>
       <c r="N386" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O386" t="n">
         <v>10</v>
@@ -40309,7 +40309,7 @@
         <v>0.003</v>
       </c>
       <c r="W526" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="X526" t="inlineStr"/>
       <c r="Y526" t="inlineStr"/>
@@ -40820,10 +40820,10 @@
         <v>0</v>
       </c>
       <c r="V532" t="n">
-        <v>0.102</v>
+        <v>0.103</v>
       </c>
       <c r="W532" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="X532" t="inlineStr"/>
       <c r="Y532" t="inlineStr"/>
@@ -41316,7 +41316,7 @@
         <v>0</v>
       </c>
       <c r="V538" t="n">
-        <v>0.15</v>
+        <v>0.148</v>
       </c>
       <c r="W538" t="n">
         <v>0.033</v>
@@ -43049,10 +43049,10 @@
         <v>0</v>
       </c>
       <c r="V559" t="n">
-        <v>0.804</v>
+        <v>0.802</v>
       </c>
       <c r="W559" t="n">
-        <v>0.763</v>
+        <v>0.76</v>
       </c>
       <c r="X559" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>0</v>
       </c>
       <c r="V560" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="W560" t="n">
         <v>0.013</v>
@@ -43223,7 +43223,7 @@
         <v>0</v>
       </c>
       <c r="V561" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="W561" t="n">
         <v>0.017</v>
@@ -44527,10 +44527,10 @@
         <v>0</v>
       </c>
       <c r="V577" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="W577" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="X577" t="inlineStr"/>
       <c r="Y577" t="inlineStr"/>
@@ -44584,10 +44584,10 @@
         <v>0.064</v>
       </c>
       <c r="N578" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O578" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P578" t="n">
         <v>2</v>
@@ -44598,10 +44598,10 @@
         </is>
       </c>
       <c r="R578" t="n">
-        <v>0.631</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="S578" t="n">
-        <v>0.764</v>
+        <v>0.847</v>
       </c>
       <c r="T578" t="n">
         <v>0</v>
@@ -45248,24 +45248,24 @@
         <v>0.092</v>
       </c>
       <c r="N586" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O586" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P586" t="n">
         <v>5</v>
       </c>
       <c r="Q586" t="inlineStr">
         <is>
-          <t>faint</t>
+          <t>found</t>
         </is>
       </c>
       <c r="R586" t="n">
-        <v>0.586</v>
+        <v>0.873</v>
       </c>
       <c r="S586" t="n">
-        <v>0.695</v>
+        <v>1</v>
       </c>
       <c r="T586" t="n">
         <v>0</v>
@@ -45274,7 +45274,7 @@
         <v>0</v>
       </c>
       <c r="V586" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="W586" t="n">
         <v>0</v>
@@ -45357,10 +45357,10 @@
         <v>0</v>
       </c>
       <c r="V587" t="n">
-        <v>0.804</v>
+        <v>0.802</v>
       </c>
       <c r="W587" t="n">
-        <v>0.789</v>
+        <v>0.787</v>
       </c>
       <c r="X587" t="inlineStr">
         <is>
@@ -45700,7 +45700,7 @@
         <v>0.007</v>
       </c>
       <c r="W591" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="X591" t="inlineStr"/>
       <c r="Y591" t="inlineStr"/>
@@ -45780,7 +45780,7 @@
         <v>0</v>
       </c>
       <c r="V592" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="W592" t="n">
         <v>0.019</v>
